--- a/data/availability/projects/the-waterway-developments/the-waterway.xlsx
+++ b/data/availability/projects/the-waterway-developments/the-waterway.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for the-waterway</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -554,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Court Yard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sea View Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1135,7 +1145,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Court Yard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1159,7 +1169,6 @@
       <c r="G2" t="n">
         <v>180</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1192,7 +1201,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Court Yard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1216,7 +1225,6 @@
       <c r="G3" t="n">
         <v>180</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1249,7 +1257,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sea View Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1273,7 +1281,6 @@
       <c r="G4" t="n">
         <v>180</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1306,7 +1313,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Court Yard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1330,7 +1337,6 @@
       <c r="G5" t="n">
         <v>185</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1363,7 +1369,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Court Yard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1387,7 +1393,6 @@
       <c r="G6" t="n">
         <v>185</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1932,7 +1937,6 @@
       <c r="G15" t="n">
         <v>85</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1943,7 +1947,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1989,7 +1993,6 @@
       <c r="G16" t="n">
         <v>85</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2000,7 +2003,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2046,7 +2049,6 @@
       <c r="G17" t="n">
         <v>85</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2057,7 +2059,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2103,7 +2105,6 @@
       <c r="G18" t="n">
         <v>135</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2114,7 +2115,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2160,7 +2161,6 @@
       <c r="G19" t="n">
         <v>140</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2217,7 +2217,6 @@
       <c r="G20" t="n">
         <v>145</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2228,7 +2227,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2289,7 +2288,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2335,7 +2334,6 @@
       <c r="G22" t="n">
         <v>175</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2346,7 +2344,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2392,7 +2390,6 @@
       <c r="G23" t="n">
         <v>175</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2403,7 +2400,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2449,7 +2446,6 @@
       <c r="G24" t="n">
         <v>175</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2460,7 +2456,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2521,7 +2517,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2567,7 +2563,6 @@
       <c r="G26" t="n">
         <v>175</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2578,7 +2573,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
